--- a/Informe_Ciberataques_Q1_2025_con_estado.xlsx
+++ b/Informe_Ciberataques_Q1_2025_con_estado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\OneDrive\Documentos\GitHub\security-dashboard-shiny\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE9DAAE-ECBE-43E9-B5A0-0E0D15E5341B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDB23C0-85DE-4603-BFA2-CC4599053DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,118 +22,118 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="38">
   <si>
-    <t>ID</t>
+    <t>Robo o filtración de datos</t>
+  </si>
+  <si>
+    <t>Accesos no autorizados</t>
+  </si>
+  <si>
+    <t>Suplantación de identidad o servicios</t>
+  </si>
+  <si>
+    <t>Uso indebido de recursos o servicios</t>
+  </si>
+  <si>
+    <t>Ataques por ingeniería social</t>
+  </si>
+  <si>
+    <t>Fallos de autenticación y control de acceso</t>
+  </si>
+  <si>
+    <t>Ataques de denegación de servicio (DoS/DDoS)</t>
+  </si>
+  <si>
+    <t>Vulnerabilidades técnicas explotadas</t>
+  </si>
+  <si>
+    <t>Filtración de datos personales en foro</t>
+  </si>
+  <si>
+    <t>Escalada de privilegios en aplicación</t>
+  </si>
+  <si>
+    <t>Web falsa imitando portal oficial</t>
+  </si>
+  <si>
+    <t>Servidor comprometido minando criptomonedas</t>
+  </si>
+  <si>
+    <t>Empleado engañado comparte credenciales</t>
+  </si>
+  <si>
+    <t>Exportación no autorizada de registros</t>
+  </si>
+  <si>
+    <t>Login sin validación de contraseña</t>
+  </si>
+  <si>
+    <t>Interrupción de servicio por tráfico anómalo</t>
+  </si>
+  <si>
+    <t>Inyección SQL detectada en formulario</t>
+  </si>
+  <si>
+    <t>XSS en comentarios de blog</t>
+  </si>
+  <si>
+    <t>Ataque DDoS desde múltiples IPs</t>
+  </si>
+  <si>
+    <t>Sesión activa sin expiración</t>
+  </si>
+  <si>
+    <t>Correo phishing con enlace falso</t>
+  </si>
+  <si>
+    <t>Correo desde dirección falsificada</t>
+  </si>
+  <si>
+    <t>Usuario externo accede a área restringida</t>
+  </si>
+  <si>
+    <t>Acceso a base de datos sin permisos</t>
+  </si>
+  <si>
+    <t>Uso de servidor para envío de spam</t>
+  </si>
+  <si>
+    <t>Muy Alto</t>
+  </si>
+  <si>
+    <t>Alto</t>
+  </si>
+  <si>
+    <t>Medio</t>
+  </si>
+  <si>
+    <t>Bajo</t>
+  </si>
+  <si>
+    <t>cerrado</t>
+  </si>
+  <si>
+    <t>descartado</t>
+  </si>
+  <si>
+    <t>en curso</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Impacto</t>
   </si>
   <si>
     <t>Categoría</t>
   </si>
   <si>
-    <t>Descripción del intento de ataque</t>
-  </si>
-  <si>
-    <t>Fecha de Detección</t>
-  </si>
-  <si>
-    <t>Estado de Resolución</t>
-  </si>
-  <si>
-    <t>Robo o filtración de datos</t>
-  </si>
-  <si>
-    <t>Accesos no autorizados</t>
-  </si>
-  <si>
-    <t>Suplantación de identidad o servicios</t>
-  </si>
-  <si>
-    <t>Uso indebido de recursos o servicios</t>
-  </si>
-  <si>
-    <t>Ataques por ingeniería social</t>
-  </si>
-  <si>
-    <t>Fallos de autenticación y control de acceso</t>
-  </si>
-  <si>
-    <t>Ataques de denegación de servicio (DoS/DDoS)</t>
-  </si>
-  <si>
-    <t>Vulnerabilidades técnicas explotadas</t>
-  </si>
-  <si>
-    <t>Filtración de datos personales en foro</t>
-  </si>
-  <si>
-    <t>Escalada de privilegios en aplicación</t>
-  </si>
-  <si>
-    <t>Web falsa imitando portal oficial</t>
-  </si>
-  <si>
-    <t>Servidor comprometido minando criptomonedas</t>
-  </si>
-  <si>
-    <t>Empleado engañado comparte credenciales</t>
-  </si>
-  <si>
-    <t>Exportación no autorizada de registros</t>
-  </si>
-  <si>
-    <t>Login sin validación de contraseña</t>
-  </si>
-  <si>
-    <t>Interrupción de servicio por tráfico anómalo</t>
-  </si>
-  <si>
-    <t>Inyección SQL detectada en formulario</t>
-  </si>
-  <si>
-    <t>XSS en comentarios de blog</t>
-  </si>
-  <si>
-    <t>Ataque DDoS desde múltiples IPs</t>
-  </si>
-  <si>
-    <t>Sesión activa sin expiración</t>
-  </si>
-  <si>
-    <t>Correo phishing con enlace falso</t>
-  </si>
-  <si>
-    <t>Correo desde dirección falsificada</t>
-  </si>
-  <si>
-    <t>Usuario externo accede a área restringida</t>
-  </si>
-  <si>
-    <t>Acceso a base de datos sin permisos</t>
-  </si>
-  <si>
-    <t>Uso de servidor para envío de spam</t>
-  </si>
-  <si>
-    <t>Muy Alto</t>
-  </si>
-  <si>
-    <t>Alto</t>
-  </si>
-  <si>
-    <t>Medio</t>
-  </si>
-  <si>
-    <t>Bajo</t>
-  </si>
-  <si>
-    <t>cerrado</t>
-  </si>
-  <si>
-    <t>descartado</t>
-  </si>
-  <si>
-    <t>en curso</t>
-  </si>
-  <si>
-    <t>Nivel de Impacto</t>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Fecha Deteccion</t>
+  </si>
+  <si>
+    <t>Estado Resolucion</t>
   </si>
 </sst>
 </file>
@@ -277,12 +277,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{312392C4-89EE-415C-999F-F672B6A08CC8}" name="Tabla2" displayName="Tabla2" ref="A1:F21" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A1:F21" xr:uid="{312392C4-89EE-415C-999F-F672B6A08CC8}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{3066030E-A621-4A80-9ABE-453EF1BBD801}" name="ID"/>
+    <tableColumn id="1" xr3:uid="{3066030E-A621-4A80-9ABE-453EF1BBD801}" name="Id"/>
     <tableColumn id="2" xr3:uid="{3838B688-37BD-4AC2-8F37-26E539A6591B}" name="Categoría"/>
-    <tableColumn id="3" xr3:uid="{8833E3FE-07E6-470F-A806-B2BE049DB2CB}" name="Descripción del intento de ataque"/>
-    <tableColumn id="4" xr3:uid="{D0495F7F-E90F-4496-9BE3-401A338ECBEA}" name="Nivel de Impacto" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{9BB74389-173D-4F19-AF54-904347C85693}" name="Fecha de Detección" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{E5F49E95-505A-46AF-A0D8-7FF084E7153D}" name="Estado de Resolución" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{8833E3FE-07E6-470F-A806-B2BE049DB2CB}" name="Descripción"/>
+    <tableColumn id="4" xr3:uid="{D0495F7F-E90F-4496-9BE3-401A338ECBEA}" name="Impacto" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{9BB74389-173D-4F19-AF54-904347C85693}" name="Fecha Deteccion" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{E5F49E95-505A-46AF-A0D8-7FF084E7153D}" name="Estado Resolucion" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -587,22 +587,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -610,19 +610,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2">
         <v>45681</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -630,19 +630,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E3" s="2">
         <v>45713</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -650,19 +650,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2">
         <v>45739</v>
       </c>
       <c r="F4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -670,19 +670,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2">
         <v>45706</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -690,19 +690,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E6" s="2">
         <v>45685</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -710,19 +710,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2">
         <v>45736</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -730,19 +730,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2">
         <v>45714</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -750,19 +750,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E9" s="2">
         <v>45694</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -770,19 +770,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E10" s="2">
         <v>45670</v>
       </c>
       <c r="F10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -790,19 +790,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E11" s="2">
         <v>45746</v>
       </c>
       <c r="F11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -810,19 +810,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E12" s="2">
         <v>45663</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -830,19 +830,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E13" s="2">
         <v>45730</v>
       </c>
       <c r="F13" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -850,19 +850,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E14" s="2">
         <v>45680</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -870,19 +870,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E15" s="2">
         <v>45734</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -890,19 +890,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E16" s="2">
         <v>45747</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -910,19 +910,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E17" s="2">
         <v>45690</v>
       </c>
       <c r="F17" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -930,19 +930,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E18" s="2">
         <v>45667</v>
       </c>
       <c r="F18" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -950,19 +950,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E19" s="2">
         <v>45696</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -970,19 +970,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E20" s="2">
         <v>45741</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -990,19 +990,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E21" s="2">
         <v>45725</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Informe_Ciberataques_Q1_2025_con_estado.xlsx
+++ b/Informe_Ciberataques_Q1_2025_con_estado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\OneDrive\Documentos\GitHub\security-dashboard-shiny\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CDB23C0-85DE-4603-BFA2-CC4599053DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{330D0ABF-5D7F-41D4-BC7C-E8244E4ACD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="38">
   <si>
     <t>Robo o filtración de datos</t>
   </si>
@@ -130,10 +130,10 @@
     <t>Descripción</t>
   </si>
   <si>
-    <t>Fecha Deteccion</t>
-  </si>
-  <si>
-    <t>Estado Resolucion</t>
+    <t>Fecha Detección</t>
+  </si>
+  <si>
+    <t>Estado Resolución</t>
   </si>
 </sst>
 </file>
@@ -274,15 +274,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{312392C4-89EE-415C-999F-F672B6A08CC8}" name="Tabla2" displayName="Tabla2" ref="A1:F21" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
-  <autoFilter ref="A1:F21" xr:uid="{312392C4-89EE-415C-999F-F672B6A08CC8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{312392C4-89EE-415C-999F-F672B6A08CC8}" name="Tabla2" displayName="Tabla2" ref="A1:F24" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
+  <autoFilter ref="A1:F24" xr:uid="{312392C4-89EE-415C-999F-F672B6A08CC8}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{3066030E-A621-4A80-9ABE-453EF1BBD801}" name="Id"/>
     <tableColumn id="2" xr3:uid="{3838B688-37BD-4AC2-8F37-26E539A6591B}" name="Categoría"/>
     <tableColumn id="3" xr3:uid="{8833E3FE-07E6-470F-A806-B2BE049DB2CB}" name="Descripción"/>
     <tableColumn id="4" xr3:uid="{D0495F7F-E90F-4496-9BE3-401A338ECBEA}" name="Impacto" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{9BB74389-173D-4F19-AF54-904347C85693}" name="Fecha Deteccion" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{E5F49E95-505A-46AF-A0D8-7FF084E7153D}" name="Estado Resolucion" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{9BB74389-173D-4F19-AF54-904347C85693}" name="Fecha Detección" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{E5F49E95-505A-46AF-A0D8-7FF084E7153D}" name="Estado Resolución" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -575,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="42.21875" bestFit="1" customWidth="1"/>
@@ -633,7 +633,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
@@ -642,7 +642,7 @@
         <v>45713</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -670,16 +670,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="2">
-        <v>45706</v>
+        <v>45713</v>
       </c>
       <c r="F5" t="s">
         <v>29</v>
@@ -690,16 +690,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2">
-        <v>45685</v>
+        <v>45706</v>
       </c>
       <c r="F6" t="s">
         <v>29</v>
@@ -710,19 +710,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2">
-        <v>45736</v>
+        <v>45685</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -730,16 +730,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2">
-        <v>45714</v>
+        <v>45736</v>
       </c>
       <c r="F8" t="s">
         <v>31</v>
@@ -750,19 +750,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" s="2">
-        <v>45694</v>
+        <v>45714</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -770,19 +770,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="2">
-        <v>45670</v>
+        <v>45694</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -790,19 +790,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2">
-        <v>45746</v>
+        <v>45670</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -813,13 +813,13 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="2">
-        <v>45663</v>
+        <v>45746</v>
       </c>
       <c r="F12" t="s">
         <v>31</v>
@@ -830,16 +830,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="2">
-        <v>45730</v>
+        <v>45663</v>
       </c>
       <c r="F13" t="s">
         <v>31</v>
@@ -853,16 +853,16 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="2">
-        <v>45680</v>
+        <v>45730</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -870,16 +870,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="2">
-        <v>45734</v>
+        <v>45680</v>
       </c>
       <c r="F15" t="s">
         <v>29</v>
@@ -890,19 +890,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
         <v>27</v>
       </c>
       <c r="E16" s="2">
-        <v>45747</v>
+        <v>45734</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -910,16 +910,16 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
         <v>27</v>
       </c>
       <c r="E17" s="2">
-        <v>45690</v>
+        <v>45747</v>
       </c>
       <c r="F17" t="s">
         <v>30</v>
@@ -930,19 +930,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" s="2">
-        <v>45667</v>
+        <v>45690</v>
       </c>
       <c r="F18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -953,16 +953,16 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="2">
-        <v>45696</v>
+        <v>45667</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -970,19 +970,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E20" s="2">
-        <v>45741</v>
+        <v>45696</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -990,19 +990,79 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="2">
+        <v>45741</v>
+      </c>
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="2">
+        <v>45741</v>
+      </c>
+      <c r="F22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
         <v>1</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C23" t="s">
         <v>9</v>
       </c>
-      <c r="D21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="2">
+      <c r="D23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="2">
         <v>45725</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F23" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="2">
+        <v>45741</v>
+      </c>
+      <c r="F24" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
